--- a/data/germination_data.xlsx
+++ b/data/germination_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temporal Ecology Lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\Project\morasoilinoculation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628D6490-0E04-4D95-8F67-7D1AFA84E6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFAE807-4571-419B-8A88-616C51B7ACED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8DD11EFF-0136-EA44-86B7-80FED636BE50}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8DD11EFF-0136-EA44-86B7-80FED636BE50}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="147">
   <si>
     <t>seed_species</t>
   </si>
@@ -504,6 +504,18 @@
   <si>
     <t>224_dead</t>
   </si>
+  <si>
+    <t>238_halfdead5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>238_alive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>238_dead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -513,20 +525,20 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -607,9 +619,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BC992C1-6373-AD4D-8EE4-164E75FC3419}" name="Table1" displayName="Table1" ref="B2:DB213" totalsRowShown="0">
-  <autoFilter ref="B2:DB213" xr:uid="{7BC992C1-6373-AD4D-8EE4-164E75FC3419}"/>
-  <tableColumns count="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BC992C1-6373-AD4D-8EE4-164E75FC3419}" name="Table1" displayName="Table1" ref="B2:DE213" totalsRowShown="0">
+  <autoFilter ref="B2:DE213" xr:uid="{7BC992C1-6373-AD4D-8EE4-164E75FC3419}"/>
+  <tableColumns count="108">
     <tableColumn id="1" xr3:uid="{1199D7AD-452C-9D4F-9453-306631F01BCC}" name="soil_species"/>
     <tableColumn id="2" xr3:uid="{11F49906-5A0D-4E4F-BA5C-F91CB62A2174}" name="seed_species"/>
     <tableColumn id="3" xr3:uid="{B695F4B4-8561-9D48-9FF3-12A40CB2B7C7}" name="inoculated_%"/>
@@ -715,6 +727,9 @@
     <tableColumn id="103" xr3:uid="{CE80CE81-DB3D-432B-8E99-37C858ECEC0B}" name="224_alive"/>
     <tableColumn id="104" xr3:uid="{796333B4-43FF-4338-B0FA-638B1B0DF92E}" name="224_dead"/>
     <tableColumn id="105" xr3:uid="{652C9F16-4173-4432-AABD-63C40291A31C}" name="224_halfdead2"/>
+    <tableColumn id="106" xr3:uid="{6C7749F0-B44E-4B7E-AF32-0332EB4C5BD4}" name="238_alive"/>
+    <tableColumn id="107" xr3:uid="{49BD0549-8B35-4807-B93D-45F954FE59A1}" name="238_dead"/>
+    <tableColumn id="108" xr3:uid="{71F4958F-D750-448B-A22F-640F39DC0079}" name="238_halfdead5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1037,15 +1052,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68F8197-A530-A948-B005-AEDF71CF4B66}">
-  <dimension ref="B2:DB214"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:DE214"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="14.09765625" customWidth="1"/>
-    <col min="4" max="4" width="17.796875" customWidth="1"/>
+    <col min="3" max="3" width="14.07421875" customWidth="1"/>
+    <col min="4" max="4" width="17.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -1361,8 +1376,17 @@
       <c r="DB2" t="s">
         <v>142</v>
       </c>
+      <c r="DC2" t="s">
+        <v>145</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>146</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="3" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -1603,8 +1627,14 @@
       <c r="DA3">
         <v>4</v>
       </c>
+      <c r="DC3">
+        <v>0</v>
+      </c>
+      <c r="DD3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="4" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -1743,8 +1773,11 @@
       <c r="CZ4">
         <v>9</v>
       </c>
+      <c r="DC4">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -1982,8 +2015,14 @@
       <c r="DA5">
         <v>7</v>
       </c>
+      <c r="DC5">
+        <v>0</v>
+      </c>
+      <c r="DD5">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -2137,8 +2176,14 @@
       <c r="DA6">
         <v>9</v>
       </c>
+      <c r="DC6">
+        <v>0</v>
+      </c>
+      <c r="DD6">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>1</v>
       </c>
@@ -2343,8 +2388,14 @@
       <c r="DA7">
         <v>6</v>
       </c>
+      <c r="DC7">
+        <v>0</v>
+      </c>
+      <c r="DD7">
+        <v>6</v>
+      </c>
     </row>
-    <row r="8" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>1</v>
       </c>
@@ -2576,8 +2627,14 @@
       <c r="DA8">
         <v>6</v>
       </c>
+      <c r="DC8">
+        <v>1</v>
+      </c>
+      <c r="DD8">
+        <v>6</v>
+      </c>
     </row>
-    <row r="9" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>1</v>
       </c>
@@ -2815,8 +2872,14 @@
       <c r="DA9">
         <v>7</v>
       </c>
+      <c r="DC9">
+        <v>0</v>
+      </c>
+      <c r="DD9">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2991,8 +3054,17 @@
       <c r="DA10">
         <v>6</v>
       </c>
+      <c r="DC10">
+        <v>1</v>
+      </c>
+      <c r="DD10">
+        <v>6</v>
+      </c>
+      <c r="DE10">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>4</v>
       </c>
@@ -3227,8 +3299,14 @@
       <c r="DA11">
         <v>8</v>
       </c>
+      <c r="DC11">
+        <v>0</v>
+      </c>
+      <c r="DD11">
+        <v>8</v>
+      </c>
     </row>
-    <row r="12" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>4</v>
       </c>
@@ -3472,8 +3550,14 @@
       <c r="DB12">
         <v>1</v>
       </c>
+      <c r="DC12">
+        <v>4</v>
+      </c>
+      <c r="DD12">
+        <v>6</v>
+      </c>
     </row>
-    <row r="13" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>4</v>
       </c>
@@ -3702,8 +3786,14 @@
       <c r="DA13">
         <v>7</v>
       </c>
+      <c r="DC13">
+        <v>0</v>
+      </c>
+      <c r="DD13">
+        <v>7</v>
+      </c>
     </row>
-    <row r="14" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>4</v>
       </c>
@@ -3899,8 +3989,17 @@
       <c r="DB14">
         <v>1</v>
       </c>
+      <c r="DC14">
+        <v>0</v>
+      </c>
+      <c r="DD14">
+        <v>8</v>
+      </c>
+      <c r="DE14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>3</v>
       </c>
@@ -4118,8 +4217,14 @@
       <c r="DA15">
         <v>8</v>
       </c>
+      <c r="DC15">
+        <v>0</v>
+      </c>
+      <c r="DD15">
+        <v>8</v>
+      </c>
     </row>
-    <row r="16" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>3</v>
       </c>
@@ -4331,8 +4436,14 @@
       <c r="DA16">
         <v>6</v>
       </c>
+      <c r="DC16">
+        <v>3</v>
+      </c>
+      <c r="DD16">
+        <v>6</v>
+      </c>
     </row>
-    <row r="17" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>3</v>
       </c>
@@ -4553,8 +4664,14 @@
       <c r="DA17">
         <v>8</v>
       </c>
+      <c r="DC17">
+        <v>0</v>
+      </c>
+      <c r="DD17">
+        <v>8</v>
+      </c>
     </row>
-    <row r="18" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4823,14 @@
       <c r="DA18">
         <v>10</v>
       </c>
+      <c r="DC18">
+        <v>0</v>
+      </c>
+      <c r="DD18">
+        <v>10</v>
+      </c>
     </row>
-    <row r="19" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>1</v>
       </c>
@@ -4946,8 +5069,14 @@
       <c r="DA19">
         <v>7</v>
       </c>
+      <c r="DC19">
+        <v>0</v>
+      </c>
+      <c r="DD19">
+        <v>7</v>
+      </c>
     </row>
-    <row r="20" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>1</v>
       </c>
@@ -5159,8 +5288,14 @@
       <c r="DB20">
         <v>1</v>
       </c>
+      <c r="DC20">
+        <v>0</v>
+      </c>
+      <c r="DD20">
+        <v>13</v>
+      </c>
     </row>
-    <row r="21" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>1</v>
       </c>
@@ -5365,8 +5500,14 @@
       <c r="DA21">
         <v>6</v>
       </c>
+      <c r="DC21">
+        <v>0</v>
+      </c>
+      <c r="DD21">
+        <v>6</v>
+      </c>
     </row>
-    <row r="22" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>1</v>
       </c>
@@ -5527,8 +5668,14 @@
       <c r="DA22">
         <v>8</v>
       </c>
+      <c r="DC22">
+        <v>0</v>
+      </c>
+      <c r="DD22">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>4</v>
       </c>
@@ -5761,8 +5908,14 @@
       <c r="DA23">
         <v>10</v>
       </c>
+      <c r="DC23">
+        <v>0</v>
+      </c>
+      <c r="DD23">
+        <v>10</v>
+      </c>
     </row>
-    <row r="24" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>4</v>
       </c>
@@ -5974,8 +6127,14 @@
       <c r="DB24">
         <v>2</v>
       </c>
+      <c r="DC24">
+        <v>1</v>
+      </c>
+      <c r="DD24">
+        <v>11</v>
+      </c>
     </row>
-    <row r="25" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>4</v>
       </c>
@@ -6130,8 +6289,14 @@
       <c r="DA25">
         <v>8</v>
       </c>
+      <c r="DC25">
+        <v>0</v>
+      </c>
+      <c r="DD25">
+        <v>8</v>
+      </c>
     </row>
-    <row r="26" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>4</v>
       </c>
@@ -6418,8 +6583,14 @@
       <c r="DA26">
         <v>11</v>
       </c>
+      <c r="DC26">
+        <v>0</v>
+      </c>
+      <c r="DD26">
+        <v>11</v>
+      </c>
     </row>
-    <row r="27" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>3</v>
       </c>
@@ -6631,8 +6802,14 @@
       <c r="DA27">
         <v>6</v>
       </c>
+      <c r="DC27">
+        <v>0</v>
+      </c>
+      <c r="DD27">
+        <v>6</v>
+      </c>
     </row>
-    <row r="28" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>3</v>
       </c>
@@ -6883,8 +7060,14 @@
       <c r="DA28">
         <v>10</v>
       </c>
+      <c r="DC28">
+        <v>0</v>
+      </c>
+      <c r="DD28">
+        <v>10</v>
+      </c>
     </row>
-    <row r="29" spans="2:106" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
         <v>3</v>
       </c>
@@ -7105,8 +7288,14 @@
       <c r="DA29" s="3">
         <v>4</v>
       </c>
+      <c r="DC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD29" s="3">
+        <v>4</v>
+      </c>
     </row>
-    <row r="30" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>3</v>
       </c>
@@ -7261,8 +7450,14 @@
       <c r="DA30">
         <v>8</v>
       </c>
+      <c r="DC30">
+        <v>0</v>
+      </c>
+      <c r="DD30">
+        <v>8</v>
+      </c>
     </row>
-    <row r="31" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>1</v>
       </c>
@@ -7501,8 +7696,14 @@
       <c r="DA31">
         <v>5</v>
       </c>
+      <c r="DC31">
+        <v>0</v>
+      </c>
+      <c r="DD31">
+        <v>5</v>
+      </c>
     </row>
-    <row r="32" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>1</v>
       </c>
@@ -7708,8 +7909,14 @@
       <c r="DA32">
         <v>10</v>
       </c>
+      <c r="DC32">
+        <v>0</v>
+      </c>
+      <c r="DD32">
+        <v>10</v>
+      </c>
     </row>
-    <row r="33" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>1</v>
       </c>
@@ -7903,8 +8110,14 @@
       <c r="DA33">
         <v>9</v>
       </c>
+      <c r="DC33">
+        <v>0</v>
+      </c>
+      <c r="DD33">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>1</v>
       </c>
@@ -8089,8 +8302,14 @@
       <c r="DA34">
         <v>6</v>
       </c>
+      <c r="DC34">
+        <v>0</v>
+      </c>
+      <c r="DD34">
+        <v>6</v>
+      </c>
     </row>
-    <row r="35" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>4</v>
       </c>
@@ -8308,8 +8527,14 @@
       <c r="DA35">
         <v>8</v>
       </c>
+      <c r="DC35">
+        <v>0</v>
+      </c>
+      <c r="DD35">
+        <v>8</v>
+      </c>
     </row>
-    <row r="36" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>4</v>
       </c>
@@ -8527,8 +8752,14 @@
       <c r="DA36">
         <v>10</v>
       </c>
+      <c r="DC36">
+        <v>0</v>
+      </c>
+      <c r="DD36">
+        <v>10</v>
+      </c>
     </row>
-    <row r="37" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>4</v>
       </c>
@@ -8689,8 +8920,14 @@
       <c r="DA37">
         <v>6</v>
       </c>
+      <c r="DC37">
+        <v>0</v>
+      </c>
+      <c r="DD37">
+        <v>6</v>
+      </c>
     </row>
-    <row r="38" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>4</v>
       </c>
@@ -8947,8 +9184,14 @@
       <c r="DA38">
         <v>6</v>
       </c>
+      <c r="DC38">
+        <v>0</v>
+      </c>
+      <c r="DD38">
+        <v>6</v>
+      </c>
     </row>
-    <row r="39" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>3</v>
       </c>
@@ -9187,8 +9430,14 @@
       <c r="DA39">
         <v>6</v>
       </c>
+      <c r="DC39">
+        <v>0</v>
+      </c>
+      <c r="DD39">
+        <v>6</v>
+      </c>
     </row>
-    <row r="40" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>3</v>
       </c>
@@ -9445,8 +9694,14 @@
       <c r="DA40">
         <v>10</v>
       </c>
+      <c r="DC40">
+        <v>0</v>
+      </c>
+      <c r="DD40">
+        <v>10</v>
+      </c>
     </row>
-    <row r="41" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>3</v>
       </c>
@@ -9661,8 +9916,14 @@
       <c r="DA41">
         <v>6</v>
       </c>
+      <c r="DC41">
+        <v>0</v>
+      </c>
+      <c r="DD41">
+        <v>6</v>
+      </c>
     </row>
-    <row r="42" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>3</v>
       </c>
@@ -9826,8 +10087,14 @@
       <c r="DA42">
         <v>7</v>
       </c>
+      <c r="DC42">
+        <v>0</v>
+      </c>
+      <c r="DD42">
+        <v>7</v>
+      </c>
     </row>
-    <row r="43" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>1</v>
       </c>
@@ -10069,8 +10336,14 @@
       <c r="DA43">
         <v>9</v>
       </c>
+      <c r="DC43">
+        <v>0</v>
+      </c>
+      <c r="DD43">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>1</v>
       </c>
@@ -10222,8 +10495,14 @@
       <c r="DA44">
         <v>6</v>
       </c>
+      <c r="DC44">
+        <v>0</v>
+      </c>
+      <c r="DD44">
+        <v>6</v>
+      </c>
     </row>
-    <row r="45" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>1</v>
       </c>
@@ -10507,8 +10786,14 @@
       <c r="DA45">
         <v>9</v>
       </c>
+      <c r="DC45">
+        <v>0</v>
+      </c>
+      <c r="DD45">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>1</v>
       </c>
@@ -10666,8 +10951,14 @@
       <c r="DA46">
         <v>6</v>
       </c>
+      <c r="DC46">
+        <v>0</v>
+      </c>
+      <c r="DD46">
+        <v>6</v>
+      </c>
     </row>
-    <row r="47" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>4</v>
       </c>
@@ -10855,8 +11146,14 @@
       <c r="DA47">
         <v>9</v>
       </c>
+      <c r="DC47">
+        <v>0</v>
+      </c>
+      <c r="DD47">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>4</v>
       </c>
@@ -11116,8 +11413,14 @@
       <c r="DA48">
         <v>11</v>
       </c>
+      <c r="DC48">
+        <v>0</v>
+      </c>
+      <c r="DD48">
+        <v>11</v>
+      </c>
     </row>
-    <row r="49" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>4</v>
       </c>
@@ -11284,8 +11587,14 @@
       <c r="DA49">
         <v>7</v>
       </c>
+      <c r="DC49">
+        <v>0</v>
+      </c>
+      <c r="DD49">
+        <v>7</v>
+      </c>
     </row>
-    <row r="50" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>4</v>
       </c>
@@ -11551,8 +11860,14 @@
       <c r="DA50">
         <v>8</v>
       </c>
+      <c r="DC50">
+        <v>0</v>
+      </c>
+      <c r="DD50">
+        <v>8</v>
+      </c>
     </row>
-    <row r="51" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>3</v>
       </c>
@@ -11800,8 +12115,14 @@
       <c r="DA51">
         <v>6</v>
       </c>
+      <c r="DC51">
+        <v>0</v>
+      </c>
+      <c r="DD51">
+        <v>6</v>
+      </c>
     </row>
-    <row r="52" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>3</v>
       </c>
@@ -11947,8 +12268,17 @@
       <c r="CZ52">
         <v>6</v>
       </c>
+      <c r="DC52">
+        <v>2</v>
+      </c>
+      <c r="DD52">
+        <v>0</v>
+      </c>
+      <c r="DE52">
+        <v>4</v>
+      </c>
     </row>
-    <row r="53" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>3</v>
       </c>
@@ -12169,8 +12499,14 @@
       <c r="DA53">
         <v>4</v>
       </c>
+      <c r="DC53">
+        <v>0</v>
+      </c>
+      <c r="DD53">
+        <v>4</v>
+      </c>
     </row>
-    <row r="54" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>3</v>
       </c>
@@ -12325,8 +12661,14 @@
       <c r="DA54">
         <v>6</v>
       </c>
+      <c r="DC54">
+        <v>0</v>
+      </c>
+      <c r="DD54">
+        <v>6</v>
+      </c>
     </row>
-    <row r="55" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>1</v>
       </c>
@@ -12550,8 +12892,14 @@
       <c r="DA55">
         <v>6</v>
       </c>
+      <c r="DC55">
+        <v>0</v>
+      </c>
+      <c r="DD55">
+        <v>6</v>
+      </c>
     </row>
-    <row r="56" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>1</v>
       </c>
@@ -12700,8 +13048,14 @@
       <c r="DB56">
         <v>3</v>
       </c>
+      <c r="DC56">
+        <v>2</v>
+      </c>
+      <c r="DD56">
+        <v>8</v>
+      </c>
     </row>
-    <row r="57" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>1</v>
       </c>
@@ -12880,8 +13234,14 @@
       <c r="DA57">
         <v>7</v>
       </c>
+      <c r="DC57">
+        <v>0</v>
+      </c>
+      <c r="DD57">
+        <v>7</v>
+      </c>
     </row>
-    <row r="58" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>1</v>
       </c>
@@ -13045,8 +13405,14 @@
       <c r="DA58">
         <v>5</v>
       </c>
+      <c r="DC58">
+        <v>1</v>
+      </c>
+      <c r="DD58">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>4</v>
       </c>
@@ -13204,8 +13570,14 @@
       <c r="DA59">
         <v>7</v>
       </c>
+      <c r="DC59">
+        <v>0</v>
+      </c>
+      <c r="DD59">
+        <v>7</v>
+      </c>
     </row>
-    <row r="60" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>4</v>
       </c>
@@ -13426,8 +13798,14 @@
       <c r="DB60">
         <v>2</v>
       </c>
+      <c r="DC60">
+        <v>1</v>
+      </c>
+      <c r="DD60">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>4</v>
       </c>
@@ -13594,8 +13972,14 @@
       <c r="DA61">
         <v>7</v>
       </c>
+      <c r="DC61">
+        <v>0</v>
+      </c>
+      <c r="DD61">
+        <v>7</v>
+      </c>
     </row>
-    <row r="62" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>4</v>
       </c>
@@ -13843,8 +14227,14 @@
       <c r="DA62">
         <v>4</v>
       </c>
+      <c r="DC62">
+        <v>1</v>
+      </c>
+      <c r="DD62">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>3</v>
       </c>
@@ -14089,8 +14479,14 @@
       <c r="DA63">
         <v>9</v>
       </c>
+      <c r="DC63">
+        <v>0</v>
+      </c>
+      <c r="DD63">
+        <v>9</v>
+      </c>
     </row>
-    <row r="64" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>3</v>
       </c>
@@ -14317,8 +14713,14 @@
       <c r="DA64">
         <v>7</v>
       </c>
+      <c r="DC64">
+        <v>3</v>
+      </c>
+      <c r="DD64">
+        <v>7</v>
+      </c>
     </row>
-    <row r="65" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>3</v>
       </c>
@@ -14536,8 +14938,14 @@
       <c r="DA65">
         <v>6</v>
       </c>
+      <c r="DC65">
+        <v>0</v>
+      </c>
+      <c r="DD65">
+        <v>6</v>
+      </c>
     </row>
-    <row r="66" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>3</v>
       </c>
@@ -14698,8 +15106,14 @@
       <c r="DA66">
         <v>5</v>
       </c>
+      <c r="DC66">
+        <v>0</v>
+      </c>
+      <c r="DD66">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>1</v>
       </c>
@@ -14947,8 +15361,14 @@
       <c r="DA67">
         <v>10</v>
       </c>
+      <c r="DC67">
+        <v>0</v>
+      </c>
+      <c r="DD67">
+        <v>10</v>
+      </c>
     </row>
-    <row r="68" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>1</v>
       </c>
@@ -15103,8 +15523,14 @@
       <c r="DB68">
         <v>1</v>
       </c>
+      <c r="DC68">
+        <v>0</v>
+      </c>
+      <c r="DD68">
+        <v>10</v>
+      </c>
     </row>
-    <row r="69" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>1</v>
       </c>
@@ -15262,8 +15688,14 @@
       <c r="DA69">
         <v>9</v>
       </c>
+      <c r="DC69">
+        <v>0</v>
+      </c>
+      <c r="DD69">
+        <v>9</v>
+      </c>
     </row>
-    <row r="70" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>1</v>
       </c>
@@ -15430,8 +15862,17 @@
       <c r="DB70">
         <v>1</v>
       </c>
+      <c r="DC70">
+        <v>0</v>
+      </c>
+      <c r="DD70">
+        <v>7</v>
+      </c>
+      <c r="DE70">
+        <v>1</v>
+      </c>
     </row>
-    <row r="71" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>4</v>
       </c>
@@ -15670,8 +16111,14 @@
       <c r="DA71">
         <v>10</v>
       </c>
+      <c r="DC71">
+        <v>0</v>
+      </c>
+      <c r="DD71">
+        <v>10</v>
+      </c>
     </row>
-    <row r="72" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>4</v>
       </c>
@@ -15898,8 +16345,14 @@
       <c r="DA72">
         <v>7</v>
       </c>
+      <c r="DC72">
+        <v>0</v>
+      </c>
+      <c r="DD72">
+        <v>7</v>
+      </c>
     </row>
-    <row r="73" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>4</v>
       </c>
@@ -16054,8 +16507,14 @@
       <c r="DA73">
         <v>10</v>
       </c>
+      <c r="DC73">
+        <v>0</v>
+      </c>
+      <c r="DD73">
+        <v>10</v>
+      </c>
     </row>
-    <row r="74" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>4</v>
       </c>
@@ -16216,8 +16675,14 @@
       <c r="DA74">
         <v>9</v>
       </c>
+      <c r="DC74">
+        <v>0</v>
+      </c>
+      <c r="DD74">
+        <v>9</v>
+      </c>
     </row>
-    <row r="75" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>3</v>
       </c>
@@ -16444,8 +16909,14 @@
       <c r="DA75">
         <v>9</v>
       </c>
+      <c r="DC75">
+        <v>0</v>
+      </c>
+      <c r="DD75">
+        <v>9</v>
+      </c>
     </row>
-    <row r="76" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>3</v>
       </c>
@@ -16696,8 +17167,14 @@
       <c r="DA76">
         <v>7</v>
       </c>
+      <c r="DC76">
+        <v>1</v>
+      </c>
+      <c r="DD76">
+        <v>7</v>
+      </c>
     </row>
-    <row r="77" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>3</v>
       </c>
@@ -16906,8 +17383,14 @@
       <c r="DA77">
         <v>7</v>
       </c>
+      <c r="DC77">
+        <v>0</v>
+      </c>
+      <c r="DD77">
+        <v>7</v>
+      </c>
     </row>
-    <row r="78" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>3</v>
       </c>
@@ -17071,8 +17554,14 @@
       <c r="DA78">
         <v>7</v>
       </c>
+      <c r="DC78">
+        <v>0</v>
+      </c>
+      <c r="DD78">
+        <v>7</v>
+      </c>
     </row>
-    <row r="79" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>1</v>
       </c>
@@ -17317,8 +17806,14 @@
       <c r="DA79">
         <v>9</v>
       </c>
+      <c r="DC79">
+        <v>0</v>
+      </c>
+      <c r="DD79">
+        <v>9</v>
+      </c>
     </row>
-    <row r="80" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>1</v>
       </c>
@@ -17536,8 +18031,14 @@
       <c r="DA80">
         <v>10</v>
       </c>
+      <c r="DC80">
+        <v>0</v>
+      </c>
+      <c r="DD80">
+        <v>10</v>
+      </c>
     </row>
-    <row r="81" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>1</v>
       </c>
@@ -17758,8 +18259,14 @@
       <c r="DA81">
         <v>7</v>
       </c>
+      <c r="DC81">
+        <v>0</v>
+      </c>
+      <c r="DD81">
+        <v>7</v>
+      </c>
     </row>
-    <row r="82" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>1</v>
       </c>
@@ -18019,8 +18526,14 @@
       <c r="DA82">
         <v>10</v>
       </c>
+      <c r="DC82">
+        <v>0</v>
+      </c>
+      <c r="DD82">
+        <v>10</v>
+      </c>
     </row>
-    <row r="83" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>4</v>
       </c>
@@ -18262,8 +18775,14 @@
       <c r="DA83">
         <v>9</v>
       </c>
+      <c r="DC83">
+        <v>0</v>
+      </c>
+      <c r="DD83">
+        <v>9</v>
+      </c>
     </row>
-    <row r="84" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>4</v>
       </c>
@@ -18505,8 +19024,14 @@
       <c r="DA84">
         <v>9</v>
       </c>
+      <c r="DC84">
+        <v>0</v>
+      </c>
+      <c r="DD84">
+        <v>9</v>
+      </c>
     </row>
-    <row r="85" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>4</v>
       </c>
@@ -18748,8 +19273,14 @@
       <c r="DA85">
         <v>6</v>
       </c>
+      <c r="DC85">
+        <v>0</v>
+      </c>
+      <c r="DD85">
+        <v>6</v>
+      </c>
     </row>
-    <row r="86" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>4</v>
       </c>
@@ -18973,8 +19504,14 @@
       <c r="DA86">
         <v>9</v>
       </c>
+      <c r="DC86">
+        <v>0</v>
+      </c>
+      <c r="DD86">
+        <v>9</v>
+      </c>
     </row>
-    <row r="87" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>3</v>
       </c>
@@ -19222,8 +19759,14 @@
       <c r="DA87">
         <v>7</v>
       </c>
+      <c r="DC87">
+        <v>0</v>
+      </c>
+      <c r="DD87">
+        <v>7</v>
+      </c>
     </row>
-    <row r="88" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>3</v>
       </c>
@@ -19453,8 +19996,14 @@
       <c r="DA88">
         <v>9</v>
       </c>
+      <c r="DC88">
+        <v>0</v>
+      </c>
+      <c r="DD88">
+        <v>9</v>
+      </c>
     </row>
-    <row r="89" spans="2:105" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="3" t="s">
         <v>3</v>
       </c>
@@ -19660,8 +20209,14 @@
       <c r="DA89" s="3">
         <v>5</v>
       </c>
+      <c r="DC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD89" s="3">
+        <v>5</v>
+      </c>
     </row>
-    <row r="90" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>3</v>
       </c>
@@ -19825,8 +20380,14 @@
       <c r="DA90">
         <v>7</v>
       </c>
+      <c r="DC90">
+        <v>0</v>
+      </c>
+      <c r="DD90">
+        <v>7</v>
+      </c>
     </row>
-    <row r="91" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>1</v>
       </c>
@@ -20080,8 +20641,14 @@
       <c r="DA91">
         <v>6</v>
       </c>
+      <c r="DC91">
+        <v>0</v>
+      </c>
+      <c r="DD91">
+        <v>6</v>
+      </c>
     </row>
-    <row r="92" spans="2:105" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:108" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="3" t="s">
         <v>1</v>
       </c>
@@ -20317,8 +20884,14 @@
       <c r="DA92" s="3">
         <v>8</v>
       </c>
+      <c r="DC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="DD92" s="3">
+        <v>8</v>
+      </c>
     </row>
-    <row r="93" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>1</v>
       </c>
@@ -20509,8 +21082,14 @@
       <c r="DA93">
         <v>9</v>
       </c>
+      <c r="DC93">
+        <v>0</v>
+      </c>
+      <c r="DD93">
+        <v>9</v>
+      </c>
     </row>
-    <row r="94" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>1</v>
       </c>
@@ -20671,8 +21250,14 @@
       <c r="DA94">
         <v>7</v>
       </c>
+      <c r="DC94">
+        <v>0</v>
+      </c>
+      <c r="DD94">
+        <v>7</v>
+      </c>
     </row>
-    <row r="95" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>4</v>
       </c>
@@ -20872,8 +21457,14 @@
       <c r="DA95">
         <v>8</v>
       </c>
+      <c r="DC95">
+        <v>0</v>
+      </c>
+      <c r="DD95">
+        <v>8</v>
+      </c>
     </row>
-    <row r="96" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>4</v>
       </c>
@@ -21100,8 +21691,14 @@
       <c r="DA96">
         <v>10</v>
       </c>
+      <c r="DC96">
+        <v>0</v>
+      </c>
+      <c r="DD96">
+        <v>10</v>
+      </c>
     </row>
-    <row r="97" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>4</v>
       </c>
@@ -21265,8 +21862,14 @@
       <c r="DA97">
         <v>8</v>
       </c>
+      <c r="DC97">
+        <v>0</v>
+      </c>
+      <c r="DD97">
+        <v>8</v>
+      </c>
     </row>
-    <row r="98" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>4</v>
       </c>
@@ -21487,8 +22090,14 @@
       <c r="DA98">
         <v>7</v>
       </c>
+      <c r="DC98">
+        <v>0</v>
+      </c>
+      <c r="DD98">
+        <v>7</v>
+      </c>
     </row>
-    <row r="99" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>3</v>
       </c>
@@ -21664,8 +22273,14 @@
       <c r="DA99">
         <v>3</v>
       </c>
+      <c r="DC99">
+        <v>0</v>
+      </c>
+      <c r="DD99">
+        <v>3</v>
+      </c>
     </row>
-    <row r="100" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>3</v>
       </c>
@@ -21814,8 +22429,14 @@
       <c r="DA100">
         <v>5</v>
       </c>
+      <c r="DC100">
+        <v>3</v>
+      </c>
+      <c r="DD100">
+        <v>5</v>
+      </c>
     </row>
-    <row r="101" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>3</v>
       </c>
@@ -22021,8 +22642,14 @@
       <c r="DA101">
         <v>5</v>
       </c>
+      <c r="DC101">
+        <v>0</v>
+      </c>
+      <c r="DD101">
+        <v>5</v>
+      </c>
     </row>
-    <row r="102" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>3</v>
       </c>
@@ -22183,8 +22810,14 @@
       <c r="DA102">
         <v>7</v>
       </c>
+      <c r="DC102">
+        <v>0</v>
+      </c>
+      <c r="DD102">
+        <v>7</v>
+      </c>
     </row>
-    <row r="103" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>1</v>
       </c>
@@ -22411,8 +23044,14 @@
       <c r="DA103">
         <v>6</v>
       </c>
+      <c r="DC103">
+        <v>0</v>
+      </c>
+      <c r="DD103">
+        <v>6</v>
+      </c>
     </row>
-    <row r="104" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>1</v>
       </c>
@@ -22636,8 +23275,14 @@
       <c r="DA104">
         <v>10</v>
       </c>
+      <c r="DC104">
+        <v>0</v>
+      </c>
+      <c r="DD104">
+        <v>10</v>
+      </c>
     </row>
-    <row r="105" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>1</v>
       </c>
@@ -22855,8 +23500,14 @@
       <c r="DA105">
         <v>6</v>
       </c>
+      <c r="DC105">
+        <v>0</v>
+      </c>
+      <c r="DD105">
+        <v>6</v>
+      </c>
     </row>
-    <row r="106" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>1</v>
       </c>
@@ -23065,8 +23716,14 @@
       <c r="DA106">
         <v>8</v>
       </c>
+      <c r="DC106">
+        <v>0</v>
+      </c>
+      <c r="DD106">
+        <v>8</v>
+      </c>
     </row>
-    <row r="107" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>4</v>
       </c>
@@ -23296,8 +23953,14 @@
       <c r="DA107">
         <v>5</v>
       </c>
+      <c r="DC107">
+        <v>0</v>
+      </c>
+      <c r="DD107">
+        <v>5</v>
+      </c>
     </row>
-    <row r="108" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>4</v>
       </c>
@@ -23512,8 +24175,14 @@
       <c r="DA108">
         <v>10</v>
       </c>
+      <c r="DC108">
+        <v>0</v>
+      </c>
+      <c r="DD108">
+        <v>10</v>
+      </c>
     </row>
-    <row r="109" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>4</v>
       </c>
@@ -23743,8 +24412,14 @@
       <c r="DA109">
         <v>9</v>
       </c>
+      <c r="DC109">
+        <v>0</v>
+      </c>
+      <c r="DD109">
+        <v>9</v>
+      </c>
     </row>
-    <row r="110" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>4</v>
       </c>
@@ -23983,8 +24658,14 @@
       <c r="DA110">
         <v>9</v>
       </c>
+      <c r="DC110">
+        <v>0</v>
+      </c>
+      <c r="DD110">
+        <v>9</v>
+      </c>
     </row>
-    <row r="111" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>3</v>
       </c>
@@ -24205,8 +24886,14 @@
       <c r="DA111">
         <v>8</v>
       </c>
+      <c r="DC111">
+        <v>0</v>
+      </c>
+      <c r="DD111">
+        <v>8</v>
+      </c>
     </row>
-    <row r="112" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>3</v>
       </c>
@@ -24433,8 +25120,14 @@
       <c r="DA112">
         <v>8</v>
       </c>
+      <c r="DC112">
+        <v>0</v>
+      </c>
+      <c r="DD112">
+        <v>8</v>
+      </c>
     </row>
-    <row r="113" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>3</v>
       </c>
@@ -24670,8 +25363,14 @@
       <c r="DA113">
         <v>6</v>
       </c>
+      <c r="DC113">
+        <v>0</v>
+      </c>
+      <c r="DD113">
+        <v>6</v>
+      </c>
     </row>
-    <row r="114" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>3</v>
       </c>
@@ -24829,8 +25528,14 @@
       <c r="DA114">
         <v>8</v>
       </c>
+      <c r="DC114">
+        <v>0</v>
+      </c>
+      <c r="DD114">
+        <v>8</v>
+      </c>
     </row>
-    <row r="115" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>1</v>
       </c>
@@ -25066,8 +25771,14 @@
       <c r="DA115">
         <v>4</v>
       </c>
+      <c r="DC115">
+        <v>0</v>
+      </c>
+      <c r="DD115">
+        <v>4</v>
+      </c>
     </row>
-    <row r="116" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>1</v>
       </c>
@@ -25288,8 +25999,14 @@
       <c r="DA116">
         <v>8</v>
       </c>
+      <c r="DC116">
+        <v>0</v>
+      </c>
+      <c r="DD116">
+        <v>8</v>
+      </c>
     </row>
-    <row r="117" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>1</v>
       </c>
@@ -25516,8 +26233,14 @@
       <c r="DA117">
         <v>5</v>
       </c>
+      <c r="DC117">
+        <v>0</v>
+      </c>
+      <c r="DD117">
+        <v>5</v>
+      </c>
     </row>
-    <row r="118" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>1</v>
       </c>
@@ -25685,8 +26408,14 @@
       <c r="DA118">
         <v>6</v>
       </c>
+      <c r="DC118">
+        <v>0</v>
+      </c>
+      <c r="DD118">
+        <v>6</v>
+      </c>
     </row>
-    <row r="119" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>4</v>
       </c>
@@ -25856,8 +26585,14 @@
       <c r="DA119">
         <v>7</v>
       </c>
+      <c r="DC119">
+        <v>0</v>
+      </c>
+      <c r="DD119">
+        <v>7</v>
+      </c>
     </row>
-    <row r="120" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>4</v>
       </c>
@@ -26018,8 +26753,14 @@
       <c r="DA120">
         <v>10</v>
       </c>
+      <c r="DC120">
+        <v>0</v>
+      </c>
+      <c r="DD120">
+        <v>10</v>
+      </c>
     </row>
-    <row r="121" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>4</v>
       </c>
@@ -26180,8 +26921,14 @@
       <c r="DA121">
         <v>8</v>
       </c>
+      <c r="DC121">
+        <v>0</v>
+      </c>
+      <c r="DD121">
+        <v>8</v>
+      </c>
     </row>
-    <row r="122" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>4</v>
       </c>
@@ -26345,8 +27092,14 @@
       <c r="DA122">
         <v>6</v>
       </c>
+      <c r="DC122">
+        <v>0</v>
+      </c>
+      <c r="DD122">
+        <v>6</v>
+      </c>
     </row>
-    <row r="123" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>3</v>
       </c>
@@ -26564,8 +27317,14 @@
       <c r="DA123">
         <v>6</v>
       </c>
+      <c r="DC123">
+        <v>0</v>
+      </c>
+      <c r="DD123">
+        <v>6</v>
+      </c>
     </row>
-    <row r="124" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>3</v>
       </c>
@@ -26825,8 +27584,14 @@
       <c r="DA124">
         <v>8</v>
       </c>
+      <c r="DC124">
+        <v>0</v>
+      </c>
+      <c r="DD124">
+        <v>8</v>
+      </c>
     </row>
-    <row r="125" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>3</v>
       </c>
@@ -27068,8 +27833,14 @@
       <c r="DA125">
         <v>6</v>
       </c>
+      <c r="DC125">
+        <v>0</v>
+      </c>
+      <c r="DD125">
+        <v>6</v>
+      </c>
     </row>
-    <row r="126" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>3</v>
       </c>
@@ -27293,8 +28064,14 @@
       <c r="DA126">
         <v>6</v>
       </c>
+      <c r="DC126">
+        <v>0</v>
+      </c>
+      <c r="DD126">
+        <v>6</v>
+      </c>
     </row>
-    <row r="127" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>1</v>
       </c>
@@ -27512,8 +28289,14 @@
       <c r="DA127">
         <v>3</v>
       </c>
+      <c r="DC127">
+        <v>0</v>
+      </c>
+      <c r="DD127">
+        <v>3</v>
+      </c>
     </row>
-    <row r="128" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>1</v>
       </c>
@@ -27662,8 +28445,14 @@
       <c r="DA128">
         <v>7</v>
       </c>
+      <c r="DC128">
+        <v>0</v>
+      </c>
+      <c r="DD128">
+        <v>7</v>
+      </c>
     </row>
-    <row r="129" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>1</v>
       </c>
@@ -27896,8 +28685,14 @@
       <c r="DA129">
         <v>6</v>
       </c>
+      <c r="DC129">
+        <v>0</v>
+      </c>
+      <c r="DD129">
+        <v>6</v>
+      </c>
     </row>
-    <row r="130" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>1</v>
       </c>
@@ -28067,8 +28862,14 @@
       <c r="DA130">
         <v>10</v>
       </c>
+      <c r="DC130">
+        <v>0</v>
+      </c>
+      <c r="DD130">
+        <v>10</v>
+      </c>
     </row>
-    <row r="131" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>4</v>
       </c>
@@ -28304,8 +29105,14 @@
       <c r="DA131">
         <v>10</v>
       </c>
+      <c r="DC131">
+        <v>0</v>
+      </c>
+      <c r="DD131">
+        <v>10</v>
+      </c>
     </row>
-    <row r="132" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>4</v>
       </c>
@@ -28463,8 +29270,14 @@
       <c r="DA132">
         <v>6</v>
       </c>
+      <c r="DC132">
+        <v>0</v>
+      </c>
+      <c r="DD132">
+        <v>6</v>
+      </c>
     </row>
-    <row r="133" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>4</v>
       </c>
@@ -28655,8 +29468,14 @@
       <c r="DA133">
         <v>7</v>
       </c>
+      <c r="DC133">
+        <v>0</v>
+      </c>
+      <c r="DD133">
+        <v>7</v>
+      </c>
     </row>
-    <row r="134" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>4</v>
       </c>
@@ -28847,8 +29666,14 @@
       <c r="DA134">
         <v>10</v>
       </c>
+      <c r="DC134">
+        <v>0</v>
+      </c>
+      <c r="DD134">
+        <v>10</v>
+      </c>
     </row>
-    <row r="135" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>3</v>
       </c>
@@ -29060,8 +29885,14 @@
       <c r="DA135">
         <v>8</v>
       </c>
+      <c r="DC135">
+        <v>0</v>
+      </c>
+      <c r="DD135">
+        <v>8</v>
+      </c>
     </row>
-    <row r="136" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>3</v>
       </c>
@@ -29267,8 +30098,14 @@
       <c r="DA136">
         <v>7</v>
       </c>
+      <c r="DC136">
+        <v>0</v>
+      </c>
+      <c r="DD136">
+        <v>7</v>
+      </c>
     </row>
-    <row r="137" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>3</v>
       </c>
@@ -29483,8 +30320,14 @@
       <c r="DA137">
         <v>5</v>
       </c>
+      <c r="DC137">
+        <v>0</v>
+      </c>
+      <c r="DD137">
+        <v>5</v>
+      </c>
     </row>
-    <row r="138" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>3</v>
       </c>
@@ -29711,8 +30554,14 @@
       <c r="DA138">
         <v>7</v>
       </c>
+      <c r="DC138">
+        <v>0</v>
+      </c>
+      <c r="DD138">
+        <v>7</v>
+      </c>
     </row>
-    <row r="139" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>1</v>
       </c>
@@ -29921,8 +30770,14 @@
       <c r="DA139">
         <v>5</v>
       </c>
+      <c r="DC139">
+        <v>0</v>
+      </c>
+      <c r="DD139">
+        <v>5</v>
+      </c>
     </row>
-    <row r="140" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>1</v>
       </c>
@@ -30086,8 +30941,14 @@
       <c r="DA140">
         <v>9</v>
       </c>
+      <c r="DC140">
+        <v>0</v>
+      </c>
+      <c r="DD140">
+        <v>9</v>
+      </c>
     </row>
-    <row r="141" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>1</v>
       </c>
@@ -30332,8 +31193,14 @@
       <c r="DA141">
         <v>8</v>
       </c>
+      <c r="DC141">
+        <v>0</v>
+      </c>
+      <c r="DD141">
+        <v>8</v>
+      </c>
     </row>
-    <row r="142" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>1</v>
       </c>
@@ -30578,8 +31445,14 @@
       <c r="DA142">
         <v>8</v>
       </c>
+      <c r="DC142">
+        <v>0</v>
+      </c>
+      <c r="DD142">
+        <v>8</v>
+      </c>
     </row>
-    <row r="143" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>4</v>
       </c>
@@ -30782,8 +31655,14 @@
       <c r="DA143">
         <v>11</v>
       </c>
+      <c r="DC143">
+        <v>0</v>
+      </c>
+      <c r="DD143">
+        <v>11</v>
+      </c>
     </row>
-    <row r="144" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>4</v>
       </c>
@@ -30938,8 +31817,14 @@
       <c r="DA144">
         <v>7</v>
       </c>
+      <c r="DC144">
+        <v>0</v>
+      </c>
+      <c r="DD144">
+        <v>7</v>
+      </c>
     </row>
-    <row r="145" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>4</v>
       </c>
@@ -31103,8 +31988,14 @@
       <c r="DA145">
         <v>5</v>
       </c>
+      <c r="DC145">
+        <v>0</v>
+      </c>
+      <c r="DD145">
+        <v>5</v>
+      </c>
     </row>
-    <row r="146" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B146" t="s">
         <v>4</v>
       </c>
@@ -31361,8 +32252,14 @@
       <c r="DA146">
         <v>10</v>
       </c>
+      <c r="DC146">
+        <v>0</v>
+      </c>
+      <c r="DD146">
+        <v>10</v>
+      </c>
     </row>
-    <row r="147" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>3</v>
       </c>
@@ -31610,8 +32507,14 @@
       <c r="DA147">
         <v>3</v>
       </c>
+      <c r="DC147">
+        <v>0</v>
+      </c>
+      <c r="DD147">
+        <v>3</v>
+      </c>
     </row>
-    <row r="148" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>3</v>
       </c>
@@ -31754,8 +32657,17 @@
       <c r="DB148">
         <v>1</v>
       </c>
+      <c r="DC148">
+        <v>6</v>
+      </c>
+      <c r="DD148">
+        <v>2</v>
+      </c>
+      <c r="DE148">
+        <v>1</v>
+      </c>
     </row>
-    <row r="149" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B149" t="s">
         <v>3</v>
       </c>
@@ -32012,8 +32924,14 @@
       <c r="DA149">
         <v>5</v>
       </c>
+      <c r="DC149">
+        <v>0</v>
+      </c>
+      <c r="DD149">
+        <v>5</v>
+      </c>
     </row>
-    <row r="150" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
         <v>3</v>
       </c>
@@ -32252,8 +33170,14 @@
       <c r="DA150">
         <v>9</v>
       </c>
+      <c r="DC150">
+        <v>0</v>
+      </c>
+      <c r="DD150">
+        <v>9</v>
+      </c>
     </row>
-    <row r="151" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B151" t="s">
         <v>1</v>
       </c>
@@ -32468,8 +33392,14 @@
       <c r="DA151">
         <v>10</v>
       </c>
+      <c r="DC151">
+        <v>0</v>
+      </c>
+      <c r="DD151">
+        <v>10</v>
+      </c>
     </row>
-    <row r="152" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
         <v>1</v>
       </c>
@@ -32621,8 +33551,14 @@
       <c r="DA152">
         <v>9</v>
       </c>
+      <c r="DC152">
+        <v>0</v>
+      </c>
+      <c r="DD152">
+        <v>9</v>
+      </c>
     </row>
-    <row r="153" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
         <v>1</v>
       </c>
@@ -32828,8 +33764,14 @@
       <c r="DA153">
         <v>7</v>
       </c>
+      <c r="DC153">
+        <v>0</v>
+      </c>
+      <c r="DD153">
+        <v>7</v>
+      </c>
     </row>
-    <row r="154" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B154" t="s">
         <v>1</v>
       </c>
@@ -33101,8 +34043,14 @@
       <c r="DA154">
         <v>8</v>
       </c>
+      <c r="DC154">
+        <v>0</v>
+      </c>
+      <c r="DD154">
+        <v>8</v>
+      </c>
     </row>
-    <row r="155" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B155" t="s">
         <v>4</v>
       </c>
@@ -33323,8 +34271,14 @@
       <c r="DA155">
         <v>9</v>
       </c>
+      <c r="DC155">
+        <v>0</v>
+      </c>
+      <c r="DD155">
+        <v>9</v>
+      </c>
     </row>
-    <row r="156" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
         <v>4</v>
       </c>
@@ -33482,8 +34436,14 @@
       <c r="DA156">
         <v>6</v>
       </c>
+      <c r="DC156">
+        <v>0</v>
+      </c>
+      <c r="DD156">
+        <v>6</v>
+      </c>
     </row>
-    <row r="157" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B157" t="s">
         <v>4</v>
       </c>
@@ -33641,8 +34601,14 @@
       <c r="DA157">
         <v>6</v>
       </c>
+      <c r="DC157">
+        <v>0</v>
+      </c>
+      <c r="DD157">
+        <v>6</v>
+      </c>
     </row>
-    <row r="158" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
         <v>4</v>
       </c>
@@ -33836,8 +34802,14 @@
       <c r="DA158">
         <v>8</v>
       </c>
+      <c r="DC158">
+        <v>0</v>
+      </c>
+      <c r="DD158">
+        <v>8</v>
+      </c>
     </row>
-    <row r="159" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
         <v>3</v>
       </c>
@@ -34073,8 +35045,14 @@
       <c r="DA159">
         <v>5</v>
       </c>
+      <c r="DC159">
+        <v>0</v>
+      </c>
+      <c r="DD159">
+        <v>5</v>
+      </c>
     </row>
-    <row r="160" spans="2:106" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:109" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
         <v>3</v>
       </c>
@@ -34226,8 +35204,14 @@
       <c r="DA160">
         <v>8</v>
       </c>
+      <c r="DC160">
+        <v>1</v>
+      </c>
+      <c r="DD160">
+        <v>8</v>
+      </c>
     </row>
-    <row r="161" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
         <v>3</v>
       </c>
@@ -34484,8 +35468,14 @@
       <c r="DA161">
         <v>7</v>
       </c>
+      <c r="DC161">
+        <v>0</v>
+      </c>
+      <c r="DD161">
+        <v>7</v>
+      </c>
     </row>
-    <row r="162" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B162" t="s">
         <v>3</v>
       </c>
@@ -34640,8 +35630,14 @@
       <c r="DA162">
         <v>8</v>
       </c>
+      <c r="DC162">
+        <v>0</v>
+      </c>
+      <c r="DD162">
+        <v>8</v>
+      </c>
     </row>
-    <row r="163" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B163" t="s">
         <v>1</v>
       </c>
@@ -34856,8 +35852,14 @@
       <c r="DA163">
         <v>8</v>
       </c>
+      <c r="DC163">
+        <v>0</v>
+      </c>
+      <c r="DD163">
+        <v>8</v>
+      </c>
     </row>
-    <row r="164" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
         <v>1</v>
       </c>
@@ -35018,8 +36020,14 @@
       <c r="DA164">
         <v>9</v>
       </c>
+      <c r="DC164">
+        <v>0</v>
+      </c>
+      <c r="DD164">
+        <v>9</v>
+      </c>
     </row>
-    <row r="165" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B165" t="s">
         <v>1</v>
       </c>
@@ -35234,8 +36242,14 @@
       <c r="DA165">
         <v>6</v>
       </c>
+      <c r="DC165">
+        <v>0</v>
+      </c>
+      <c r="DD165">
+        <v>6</v>
+      </c>
     </row>
-    <row r="166" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
         <v>1</v>
       </c>
@@ -35435,8 +36449,14 @@
       <c r="DA166">
         <v>6</v>
       </c>
+      <c r="DC166">
+        <v>0</v>
+      </c>
+      <c r="DD166">
+        <v>6</v>
+      </c>
     </row>
-    <row r="167" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
         <v>4</v>
       </c>
@@ -35639,8 +36659,14 @@
       <c r="DA167">
         <v>8</v>
       </c>
+      <c r="DC167">
+        <v>0</v>
+      </c>
+      <c r="DD167">
+        <v>8</v>
+      </c>
     </row>
-    <row r="168" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B168" t="s">
         <v>4</v>
       </c>
@@ -35876,8 +36902,14 @@
       <c r="DA168">
         <v>11</v>
       </c>
+      <c r="DC168">
+        <v>0</v>
+      </c>
+      <c r="DD168">
+        <v>11</v>
+      </c>
     </row>
-    <row r="169" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
         <v>4</v>
       </c>
@@ -36035,8 +37067,14 @@
       <c r="DA169">
         <v>6</v>
       </c>
+      <c r="DC169">
+        <v>0</v>
+      </c>
+      <c r="DD169">
+        <v>6</v>
+      </c>
     </row>
-    <row r="170" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B170" t="s">
         <v>4</v>
       </c>
@@ -36218,8 +37256,14 @@
       <c r="DA170">
         <v>8</v>
       </c>
+      <c r="DC170">
+        <v>0</v>
+      </c>
+      <c r="DD170">
+        <v>8</v>
+      </c>
     </row>
-    <row r="171" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
         <v>3</v>
       </c>
@@ -36464,8 +37508,14 @@
       <c r="DA171">
         <v>10</v>
       </c>
+      <c r="DC171">
+        <v>0</v>
+      </c>
+      <c r="DD171">
+        <v>10</v>
+      </c>
     </row>
-    <row r="172" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
         <v>3</v>
       </c>
@@ -36629,8 +37679,14 @@
       <c r="DA172">
         <v>8</v>
       </c>
+      <c r="DC172">
+        <v>0</v>
+      </c>
+      <c r="DD172">
+        <v>8</v>
+      </c>
     </row>
-    <row r="173" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
         <v>3</v>
       </c>
@@ -36809,8 +37865,14 @@
       <c r="DA173">
         <v>8</v>
       </c>
+      <c r="DC173">
+        <v>0</v>
+      </c>
+      <c r="DD173">
+        <v>8</v>
+      </c>
     </row>
-    <row r="174" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B174" t="s">
         <v>3</v>
       </c>
@@ -36974,8 +38036,14 @@
       <c r="DA174">
         <v>9</v>
       </c>
+      <c r="DC174">
+        <v>0</v>
+      </c>
+      <c r="DD174">
+        <v>9</v>
+      </c>
     </row>
-    <row r="175" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>1</v>
       </c>
@@ -37196,8 +38264,14 @@
       <c r="DA175">
         <v>9</v>
       </c>
+      <c r="DC175">
+        <v>0</v>
+      </c>
+      <c r="DD175">
+        <v>9</v>
+      </c>
     </row>
-    <row r="176" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
         <v>1</v>
       </c>
@@ -37352,8 +38426,14 @@
       <c r="DA176">
         <v>8</v>
       </c>
+      <c r="DC176">
+        <v>0</v>
+      </c>
+      <c r="DD176">
+        <v>8</v>
+      </c>
     </row>
-    <row r="177" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>1</v>
       </c>
@@ -37517,8 +38597,14 @@
       <c r="DA177">
         <v>5</v>
       </c>
+      <c r="DC177">
+        <v>0</v>
+      </c>
+      <c r="DD177">
+        <v>5</v>
+      </c>
     </row>
-    <row r="178" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>1</v>
       </c>
@@ -37688,8 +38774,14 @@
       <c r="DA178">
         <v>8</v>
       </c>
+      <c r="DC178">
+        <v>0</v>
+      </c>
+      <c r="DD178">
+        <v>8</v>
+      </c>
     </row>
-    <row r="179" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>4</v>
       </c>
@@ -37910,8 +39002,14 @@
       <c r="DA179">
         <v>10</v>
       </c>
+      <c r="DC179">
+        <v>0</v>
+      </c>
+      <c r="DD179">
+        <v>10</v>
+      </c>
     </row>
-    <row r="180" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>4</v>
       </c>
@@ -38129,8 +39227,14 @@
       <c r="DA180">
         <v>9</v>
       </c>
+      <c r="DC180">
+        <v>0</v>
+      </c>
+      <c r="DD180">
+        <v>9</v>
+      </c>
     </row>
-    <row r="181" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B181" t="s">
         <v>4</v>
       </c>
@@ -38348,8 +39452,14 @@
       <c r="DA181">
         <v>9</v>
       </c>
+      <c r="DC181">
+        <v>0</v>
+      </c>
+      <c r="DD181">
+        <v>9</v>
+      </c>
     </row>
-    <row r="182" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>4</v>
       </c>
@@ -38510,8 +39620,14 @@
       <c r="DA182">
         <v>6</v>
       </c>
+      <c r="DC182">
+        <v>0</v>
+      </c>
+      <c r="DD182">
+        <v>6</v>
+      </c>
     </row>
-    <row r="183" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>3</v>
       </c>
@@ -38761,8 +39877,14 @@
       <c r="DA183">
         <v>5</v>
       </c>
+      <c r="DC183">
+        <v>0</v>
+      </c>
+      <c r="DD183">
+        <v>5</v>
+      </c>
     </row>
-    <row r="184" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>1</v>
       </c>
@@ -38931,8 +40053,14 @@
       <c r="DA184">
         <v>6</v>
       </c>
+      <c r="DC184">
+        <v>0</v>
+      </c>
+      <c r="DD184">
+        <v>6</v>
+      </c>
     </row>
-    <row r="185" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>3</v>
       </c>
@@ -39152,8 +40280,14 @@
       <c r="DA185">
         <v>7</v>
       </c>
+      <c r="DC185">
+        <v>0</v>
+      </c>
+      <c r="DD185">
+        <v>7</v>
+      </c>
     </row>
-    <row r="186" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>1</v>
       </c>
@@ -39361,8 +40495,14 @@
       <c r="DA186">
         <v>2</v>
       </c>
+      <c r="DC186">
+        <v>5</v>
+      </c>
+      <c r="DD186">
+        <v>2</v>
+      </c>
     </row>
-    <row r="187" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>4</v>
       </c>
@@ -39540,8 +40680,14 @@
       <c r="DA187">
         <v>8</v>
       </c>
+      <c r="DC187">
+        <v>0</v>
+      </c>
+      <c r="DD187">
+        <v>8</v>
+      </c>
     </row>
-    <row r="188" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>4</v>
       </c>
@@ -39773,8 +40919,14 @@
       <c r="DA188">
         <v>10</v>
       </c>
+      <c r="DC188">
+        <v>0</v>
+      </c>
+      <c r="DD188">
+        <v>10</v>
+      </c>
     </row>
-    <row r="189" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
         <v>3</v>
       </c>
@@ -40000,8 +41152,14 @@
       <c r="DA189">
         <v>2</v>
       </c>
+      <c r="DC189">
+        <v>0</v>
+      </c>
+      <c r="DD189">
+        <v>2</v>
+      </c>
     </row>
-    <row r="190" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>1</v>
       </c>
@@ -40230,8 +41388,14 @@
       <c r="DA190">
         <v>5</v>
       </c>
+      <c r="DC190">
+        <v>0</v>
+      </c>
+      <c r="DD190">
+        <v>5</v>
+      </c>
     </row>
-    <row r="191" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>3</v>
       </c>
@@ -40463,8 +41627,14 @@
       <c r="DA191">
         <v>5</v>
       </c>
+      <c r="DC191">
+        <v>0</v>
+      </c>
+      <c r="DD191">
+        <v>5</v>
+      </c>
     </row>
-    <row r="192" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>1</v>
       </c>
@@ -40675,8 +41845,14 @@
       <c r="DA192">
         <v>3</v>
       </c>
+      <c r="DC192">
+        <v>0</v>
+      </c>
+      <c r="DD192">
+        <v>3</v>
+      </c>
     </row>
-    <row r="193" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>4</v>
       </c>
@@ -40911,8 +42087,14 @@
       <c r="DA193">
         <v>7</v>
       </c>
+      <c r="DC193">
+        <v>0</v>
+      </c>
+      <c r="DD193">
+        <v>7</v>
+      </c>
     </row>
-    <row r="194" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
         <v>4</v>
       </c>
@@ -41123,8 +42305,14 @@
       <c r="DA194">
         <v>7</v>
       </c>
+      <c r="DC194">
+        <v>0</v>
+      </c>
+      <c r="DD194">
+        <v>7</v>
+      </c>
     </row>
-    <row r="195" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B195" t="s">
         <v>3</v>
       </c>
@@ -41350,8 +42538,14 @@
       <c r="DA195">
         <v>2</v>
       </c>
+      <c r="DC195">
+        <v>0</v>
+      </c>
+      <c r="DD195">
+        <v>2</v>
+      </c>
     </row>
-    <row r="196" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>1</v>
       </c>
@@ -41610,8 +42804,14 @@
       <c r="DA196">
         <v>9</v>
       </c>
+      <c r="DC196">
+        <v>0</v>
+      </c>
+      <c r="DD196">
+        <v>9</v>
+      </c>
     </row>
-    <row r="197" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B197" t="s">
         <v>3</v>
       </c>
@@ -41825,8 +43025,14 @@
       <c r="DA197">
         <v>4</v>
       </c>
+      <c r="DC197">
+        <v>0</v>
+      </c>
+      <c r="DD197">
+        <v>4</v>
+      </c>
     </row>
-    <row r="198" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>1</v>
       </c>
@@ -42022,8 +43228,14 @@
       <c r="DA198">
         <v>5</v>
       </c>
+      <c r="DC198">
+        <v>0</v>
+      </c>
+      <c r="DD198">
+        <v>5</v>
+      </c>
     </row>
-    <row r="199" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
         <v>4</v>
       </c>
@@ -42231,8 +43443,14 @@
       <c r="DA199">
         <v>6</v>
       </c>
+      <c r="DC199">
+        <v>0</v>
+      </c>
+      <c r="DD199">
+        <v>6</v>
+      </c>
     </row>
-    <row r="200" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
         <v>4</v>
       </c>
@@ -42437,8 +43655,14 @@
       <c r="DA200">
         <v>7</v>
       </c>
+      <c r="DC200">
+        <v>0</v>
+      </c>
+      <c r="DD200">
+        <v>7</v>
+      </c>
     </row>
-    <row r="201" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B201" t="s">
         <v>3</v>
       </c>
@@ -42679,8 +43903,14 @@
       <c r="DA201">
         <v>6</v>
       </c>
+      <c r="DC201">
+        <v>0</v>
+      </c>
+      <c r="DD201">
+        <v>6</v>
+      </c>
     </row>
-    <row r="202" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>1</v>
       </c>
@@ -42912,8 +44142,14 @@
       <c r="DA202">
         <v>1</v>
       </c>
+      <c r="DC202">
+        <v>0</v>
+      </c>
+      <c r="DD202">
+        <v>1</v>
+      </c>
     </row>
-    <row r="203" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
         <v>3</v>
       </c>
@@ -43139,8 +44375,14 @@
       <c r="DA203">
         <v>3</v>
       </c>
+      <c r="DC203">
+        <v>0</v>
+      </c>
+      <c r="DD203">
+        <v>3</v>
+      </c>
     </row>
-    <row r="204" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
         <v>1</v>
       </c>
@@ -43270,8 +44512,11 @@
       <c r="CZ204">
         <v>6</v>
       </c>
+      <c r="DC204">
+        <v>6</v>
+      </c>
     </row>
-    <row r="205" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
         <v>4</v>
       </c>
@@ -43518,8 +44763,14 @@
       <c r="DA205">
         <v>8</v>
       </c>
+      <c r="DC205">
+        <v>0</v>
+      </c>
+      <c r="DD205">
+        <v>10</v>
+      </c>
     </row>
-    <row r="206" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
         <v>4</v>
       </c>
@@ -43670,8 +44921,14 @@
       <c r="DA206">
         <v>6</v>
       </c>
+      <c r="DC206">
+        <v>0</v>
+      </c>
+      <c r="DD206">
+        <v>6</v>
+      </c>
     </row>
-    <row r="207" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
         <v>3</v>
       </c>
@@ -43870,8 +45127,14 @@
       <c r="DA207">
         <v>4</v>
       </c>
+      <c r="DC207">
+        <v>0</v>
+      </c>
+      <c r="DD207">
+        <v>4</v>
+      </c>
     </row>
-    <row r="208" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>1</v>
       </c>
@@ -44097,8 +45360,14 @@
       <c r="DA208">
         <v>3</v>
       </c>
+      <c r="DC208">
+        <v>0</v>
+      </c>
+      <c r="DD208">
+        <v>3</v>
+      </c>
     </row>
-    <row r="209" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
         <v>3</v>
       </c>
@@ -44309,8 +45578,14 @@
       <c r="DA209">
         <v>5</v>
       </c>
+      <c r="DC209">
+        <v>0</v>
+      </c>
+      <c r="DD209">
+        <v>5</v>
+      </c>
     </row>
-    <row r="210" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>1</v>
       </c>
@@ -44545,8 +45820,14 @@
       <c r="DA210">
         <v>5</v>
       </c>
+      <c r="DC210">
+        <v>0</v>
+      </c>
+      <c r="DD210">
+        <v>5</v>
+      </c>
     </row>
-    <row r="211" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
         <v>4</v>
       </c>
@@ -44757,8 +46038,14 @@
       <c r="DA211">
         <v>4</v>
       </c>
+      <c r="DC211">
+        <v>0</v>
+      </c>
+      <c r="DD211">
+        <v>5</v>
+      </c>
     </row>
-    <row r="212" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:108" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
         <v>4</v>
       </c>
@@ -44963,8 +46250,14 @@
       <c r="DA212">
         <v>6</v>
       </c>
+      <c r="DC212">
+        <v>0</v>
+      </c>
+      <c r="DD212">
+        <v>6</v>
+      </c>
     </row>
-    <row r="214" spans="2:105" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:108" x14ac:dyDescent="0.35">
       <c r="DA214" t="s">
         <v>140</v>
       </c>
